--- a/MCF Languages_with_scores1.xlsx
+++ b/MCF Languages_with_scores1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\audio_transscript\gemnai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\asr_transcriibe_script\asr_transcribe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FDC762-AD95-4E10-91FC-5F05AA015FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AB3A7E-EAA2-4874-BD28-47025608CD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pidgin" sheetId="1" r:id="rId1"/>
@@ -2100,6 +2100,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="13" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2475,6 +2495,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="14" max="14" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2859,6 +2899,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AE4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="14" max="14" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="35.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
